--- a/OUT_EXCEL/out_1.xlsx
+++ b/OUT_EXCEL/out_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,24 +438,20 @@
       <c r="D1" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Năm 2024</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nam 2024</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Nam 2023</t>
+          <t>Năm 2023</t>
         </is>
       </c>
     </row>
@@ -464,15 +460,14 @@
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Triệu đồng</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Trieu dong</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Trieu dong</t>
+          <t>Triệu đồng</t>
         </is>
       </c>
     </row>
@@ -480,31 +475,29 @@
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LUUCHUYEN TIEN TUHOAT DONG DAU TU</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LƯU CHUYỄN TIỀN TỪ HOẠT ĐỘNG ĐẢU TƯ'</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>01 Mua sắm tài sản có đjnh</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>01 Mua sam tai san co djnh</t>
+          <t>(919.740)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>(919.740)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
         <is>
           <t>(1.276.249)</t>
         </is>
@@ -514,18 +507,17 @@
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>02  Tièn thu tử thanh lý, nhượng bán tài sản cố đinh</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>02 Tien thu tr thanh ly,nhuong ban tai san co dinh</t>
+          <t>147.865</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>147.865</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
         <is>
           <t>4.038</t>
         </is>
@@ -535,74 +527,85 @@
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>05 Tiền thu từ bán; thanh lý bất động sản đẳu tư</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>05 Tien thu tr ban, thanh ly bat dong san dau tu</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>07 Tien chi dau tu, gop von vao cac don vj khac</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>07 Tiên chi đầu tư, góp vón vào các đơn vỉ khác</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>08 Tiền thu đằu tư , góp vốn vào các đơn vi khác</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>08 Tien thu dau tu,gop von vao cac don vj khac</t>
+          <t>3.506</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.506</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>=</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>09 Tien thu co turc va loi nhuan duoc chia tr cac khoan dau tu,</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>09 Tiền thu co tức vả lợi nhuận được chia tử các khoản đầu tư ,</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>góp vốn dài han</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gop von dai han</t>
+          <t>35.058</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>35.058</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
         <is>
           <t>74.955</t>
         </is>
@@ -612,18 +615,17 @@
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>II   LUU CHUYEN TIỀN THUAN TỪ HOẠT ĐỘNG ĐẢU TƯ'</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LUUCHUYENTIEN THUAN TUHOAT DONG DAU TU</t>
+          <t>(733.311)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
-        <is>
-          <t>(733.311)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
         <is>
           <t>(1.197.256)</t>
         </is>
@@ -633,83 +635,85 @@
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LUUCHUYEN TIEN TUHOAT DONG TAICHiNH</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LUU CHUYỂN TIỀN TỪ HOẠT ĐỘNG TÀl CHÍNH</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>02 Tien thu tr phat hanh giay to co gia dai han co du dieu kien tinh</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>02 Tiền thu từ phát hành giấy tờ có giá dảỉ han có đủ đĩèu kiện tính</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>vao vốn tự có và các khoán vốn vay dài hạn khác</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>vao von tu co va cac khoan von vay dai han khac</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>03 Tien chi thanh toan giay toco gia dai han co du dieu kien tinh</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>03 Tiền chi thanh toán giấy tờ có giá dài hạn có đủ điều kiện tính</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>vao von ty co va cac khoan von vay dai han khac</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>vào vốn tự có và các khoản vốn vay dài hạn khác</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>04 Cỗ tức đã trả cho các cỗ đông; lợi nhuận đẳ chia</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>04 Co turc da tra cho cac co dong,loi nhuan da chia</t>
+          <t>(3.884.051)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
-        <is>
-          <t>3.884.051)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
         <is>
           <t>(3.377.435)</t>
         </is>
@@ -721,20 +725,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>III   LUU CHUYẺN TIẺN THUẢN TỪ HOẠT ĐỘNG TÀI CHÍNH</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LUUCHUYEN TIEN THUAN TUHOAT DONG TAICHINH</t>
+          <t>(3.884.051)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
-        <is>
-          <t>3.884.051)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
         <is>
           <t>(3.377.435)</t>
         </is>
@@ -746,20 +745,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>IV LUU CHUYEN TIỀN THUAN TRONG KỲ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LUU CHUYEN TIEN THUAN TRONG KY</t>
+          <t>3.752.870</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
-        <is>
-          <t>3.752.870</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
         <is>
           <t>32.561.510</t>
         </is>
@@ -771,33 +765,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>TIEN VA CAC KHOAN TUONG DUONG TIEN TAINGAY</t>
-        </is>
-      </c>
+          <t>V TIỀN VÀ CÁC KHOẢN TUƠNG ĐƯƠNG TIỀN TẠI NGÀY</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1 THÁNG 1</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1THANG1</t>
+          <t>136.071.738</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
-        <is>
-          <t>136.071.738</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
         <is>
           <t>103.510.228</t>
         </is>
@@ -807,44 +795,49 @@
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>VI   Điều chỉnh ảnh hưởng của thay đổi tỷ giá</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>VI Dieu chinh anh huong cua thay doi ty gia</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>VII TIEN VA CAC KHOAN TUONG DUONG TIEN TAINGAY 31</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>VII TIỀN VÀ CÁC KHOẢN TƯƠNG ĐƯƠNG TIỀN TẠI NGÀY 31</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>THẢNG 12</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>THANG 12</t>
+          <t>139.824.608</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
-        <is>
-          <t>139.824.608</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
         <is>
           <t>136.071.738</t>
         </is>
@@ -854,31 +847,29 @@
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Tien va cac khoan tuong duong tien gom co:</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tiền và các khoản tương đương tiền gồm có:</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>-Tiền mặt; vàng bac, đá quý</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-Tien mat, vang bac, da quy</t>
+          <t>5.696.449</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
-        <is>
-          <t>5.696.449</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
         <is>
           <t>6.909.300</t>
         </is>
@@ -888,18 +879,17 @@
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>-Tiền gửi thanh toán tại Ngân hàng Nhà nước</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-Tien guri thanh toan tai Ngan hang Nha nuoc</t>
+          <t>25.219.753</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
-        <is>
-          <t>25.219.753</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
         <is>
           <t>18.504.814</t>
         </is>
@@ -909,18 +899,17 @@
       <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>-Tièn gửi tại các tố chức tín dung khác</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-Tien guri tai cac to churc tin dung khac</t>
+          <t>107.908.406</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
-        <is>
-          <t>107.908.406</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
         <is>
           <t>110.421.734</t>
         </is>
@@ -930,18 +919,17 @@
       <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>-Chứng khoán đằu tư</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-Chtrng khoan dau tu</t>
+          <t>1,OOO 00O</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
-        <is>
-          <t>1.000.000</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
         <is>
           <t>235.890</t>
         </is>
